--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/after_conversion_caes2014_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/after_conversion_caes2014_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="84">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Jefferson</t>
@@ -626,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AE43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -652,9 +655,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,13 +749,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2">
         <v>43.64283</v>
@@ -802,12 +809,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>44.14558</v>
@@ -858,12 +865,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>44.14166</v>
@@ -914,12 +921,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5">
         <v>43.79211</v>
@@ -970,12 +977,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <v>44.09325</v>
@@ -1029,12 +1036,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7">
         <v>43.33278</v>
@@ -1085,12 +1092,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>43.60234</v>
@@ -1144,12 +1151,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9">
         <v>42.6994</v>
@@ -1203,12 +1210,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>42.64497</v>
@@ -1262,12 +1269,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>42.64432</v>
@@ -1321,12 +1328,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>42.69457</v>
@@ -1377,12 +1384,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>42.54479</v>
@@ -1436,12 +1443,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>42.54348</v>
@@ -1492,12 +1499,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15">
         <v>42.58318</v>
@@ -1551,12 +1558,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16">
         <v>43.44244</v>
@@ -1609,10 +1616,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17">
         <v>43.43774</v>
@@ -1665,10 +1672,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18">
         <v>43.43142</v>
@@ -1721,10 +1728,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C19">
         <v>43.43121</v>
@@ -1777,10 +1784,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>43.64283</v>
@@ -1806,10 +1813,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21">
         <v>42.10207</v>
@@ -1859,10 +1866,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22">
         <v>42.11042</v>
@@ -1912,10 +1919,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23">
         <v>42.08359</v>
@@ -1965,10 +1972,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24">
         <v>42.09787</v>
@@ -2018,10 +2025,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25">
         <v>42.72589</v>
@@ -2074,10 +2081,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26">
         <v>42.23667</v>
@@ -2130,10 +2137,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27">
         <v>42.107989</v>
@@ -2186,10 +2193,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28">
         <v>42.10776</v>
@@ -2242,10 +2249,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29">
         <v>42.09656</v>
@@ -2298,10 +2305,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30">
         <v>43.36414</v>
@@ -2354,10 +2361,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31">
         <v>43.42818</v>
@@ -2410,10 +2417,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32">
         <v>43.42341</v>
@@ -2463,10 +2470,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33">
         <v>43.42322</v>
@@ -2516,10 +2523,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C34">
         <v>43.29241</v>
@@ -2569,10 +2576,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C35">
         <v>43.3829</v>
@@ -2622,10 +2629,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C36">
         <v>43.32777</v>
@@ -2678,10 +2685,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C37">
         <v>43.12966</v>
@@ -2731,10 +2738,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C38">
         <v>42.17334</v>
@@ -2784,10 +2791,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39">
         <v>42.08533</v>
@@ -2840,10 +2847,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C40">
         <v>42.47663</v>
@@ -2896,10 +2903,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41">
         <v>42.70399</v>
@@ -2949,10 +2956,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>42.68841</v>
@@ -3002,10 +3009,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C43">
         <v>42.68841</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/after_conversion_caes2014_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/CAES2024_Datenbank/after_conversion_caes2014_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="85">
   <si>
     <t>location</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Banbury Hot Springs</t>
+  </si>
+  <si>
+    <t>Basalt</t>
   </si>
 </sst>
 </file>
@@ -766,6 +769,9 @@
       <c r="D2">
         <v>-111.68768</v>
       </c>
+      <c r="F2" t="s">
+        <v>84</v>
+      </c>
       <c r="H2">
         <v>48.2</v>
       </c>
@@ -822,6 +828,9 @@
       <c r="D3">
         <v>-112.55494</v>
       </c>
+      <c r="F3" t="s">
+        <v>84</v>
+      </c>
       <c r="H3">
         <v>56.1</v>
       </c>
@@ -878,6 +887,9 @@
       <c r="D4">
         <v>-112.5524</v>
       </c>
+      <c r="F4" t="s">
+        <v>84</v>
+      </c>
       <c r="H4">
         <v>52.3</v>
       </c>
@@ -934,6 +946,9 @@
       <c r="D5">
         <v>-111.44009</v>
       </c>
+      <c r="F5" t="s">
+        <v>84</v>
+      </c>
       <c r="H5">
         <v>44</v>
       </c>
@@ -993,6 +1008,9 @@
       <c r="E6">
         <v>1216.7616</v>
       </c>
+      <c r="F6" t="s">
+        <v>84</v>
+      </c>
       <c r="H6">
         <v>31.4</v>
       </c>
@@ -1049,6 +1067,9 @@
       <c r="D7">
         <v>-113.9179</v>
       </c>
+      <c r="F7" t="s">
+        <v>84</v>
+      </c>
       <c r="H7">
         <v>50.5</v>
       </c>
@@ -1108,6 +1129,9 @@
       <c r="E8">
         <v>272.1864</v>
       </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
       <c r="H8">
         <v>36.3</v>
       </c>
@@ -1167,6 +1191,9 @@
       <c r="E9">
         <v>243.84</v>
       </c>
+      <c r="F9" t="s">
+        <v>84</v>
+      </c>
       <c r="H9">
         <v>24.7</v>
       </c>
@@ -1226,6 +1253,9 @@
       <c r="E10">
         <v>327.66</v>
       </c>
+      <c r="F10" t="s">
+        <v>84</v>
+      </c>
       <c r="H10">
         <v>34.5</v>
       </c>
@@ -1285,6 +1315,9 @@
       <c r="E11">
         <v>320.04</v>
       </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
       <c r="H11">
         <v>34.4</v>
       </c>
@@ -1341,6 +1374,9 @@
       <c r="D12">
         <v>-114.85592</v>
       </c>
+      <c r="F12" t="s">
+        <v>84</v>
+      </c>
       <c r="H12">
         <v>58.4</v>
       </c>
@@ -1400,6 +1436,9 @@
       <c r="E13">
         <v>445.008</v>
       </c>
+      <c r="F13" t="s">
+        <v>84</v>
+      </c>
       <c r="H13">
         <v>37.5</v>
       </c>
@@ -1456,6 +1495,9 @@
       <c r="D14">
         <v>-114.94897</v>
       </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
       <c r="H14">
         <v>36.2</v>
       </c>
@@ -1515,6 +1557,9 @@
       <c r="E15">
         <v>451.104</v>
       </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
       <c r="H15">
         <v>38.1</v>
       </c>
@@ -1571,6 +1616,9 @@
       <c r="D16">
         <v>-111.90484</v>
       </c>
+      <c r="F16" t="s">
+        <v>84</v>
+      </c>
       <c r="H16">
         <v>20.9</v>
       </c>
@@ -1627,6 +1675,9 @@
       <c r="D17">
         <v>-111.93018</v>
       </c>
+      <c r="F17" t="s">
+        <v>84</v>
+      </c>
       <c r="H17">
         <v>27.7</v>
       </c>
@@ -1683,6 +1734,9 @@
       <c r="D18">
         <v>-111.94501</v>
       </c>
+      <c r="F18" t="s">
+        <v>84</v>
+      </c>
       <c r="H18">
         <v>26.8</v>
       </c>
@@ -1739,6 +1793,9 @@
       <c r="D19">
         <v>-111.94469</v>
       </c>
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
       <c r="H19">
         <v>25.1</v>
       </c>
@@ -1795,6 +1852,9 @@
       <c r="D20">
         <v>-111.68768</v>
       </c>
+      <c r="F20" t="s">
+        <v>84</v>
+      </c>
       <c r="H20">
         <v>48.6</v>
       </c>
@@ -1824,6 +1884,9 @@
       <c r="D21">
         <v>-113.38434</v>
       </c>
+      <c r="F21" t="s">
+        <v>84</v>
+      </c>
       <c r="H21">
         <v>59.7</v>
       </c>
@@ -1877,6 +1940,9 @@
       <c r="D22">
         <v>-113.37519</v>
       </c>
+      <c r="F22" t="s">
+        <v>84</v>
+      </c>
       <c r="H22">
         <v>47.9</v>
       </c>
@@ -1930,6 +1996,9 @@
       <c r="D23">
         <v>-113.35865</v>
       </c>
+      <c r="F23" t="s">
+        <v>84</v>
+      </c>
       <c r="H23">
         <v>48</v>
       </c>
@@ -1983,6 +2052,9 @@
       <c r="D24">
         <v>-113.38541</v>
       </c>
+      <c r="F24" t="s">
+        <v>84</v>
+      </c>
       <c r="H24">
         <v>48.3</v>
       </c>
@@ -2036,6 +2108,9 @@
       <c r="D25">
         <v>-112.87381</v>
       </c>
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
       <c r="H25">
         <v>32.7</v>
       </c>
@@ -2092,6 +2167,9 @@
       <c r="D26">
         <v>-113.36971</v>
       </c>
+      <c r="F26" t="s">
+        <v>84</v>
+      </c>
       <c r="H26">
         <v>54.7</v>
       </c>
@@ -2148,6 +2226,9 @@
       <c r="D27">
         <v>-113.39206</v>
       </c>
+      <c r="F27" t="s">
+        <v>84</v>
+      </c>
       <c r="H27">
         <v>44.7</v>
       </c>
@@ -2204,6 +2285,9 @@
       <c r="D28">
         <v>-113.39186</v>
       </c>
+      <c r="F28" t="s">
+        <v>84</v>
+      </c>
       <c r="H28">
         <v>40.9</v>
       </c>
@@ -2260,6 +2344,9 @@
       <c r="D29">
         <v>-113.378</v>
       </c>
+      <c r="F29" t="s">
+        <v>84</v>
+      </c>
       <c r="H29">
         <v>26</v>
       </c>
@@ -2316,6 +2403,9 @@
       <c r="D30">
         <v>-113.78943</v>
       </c>
+      <c r="F30" t="s">
+        <v>84</v>
+      </c>
       <c r="H30">
         <v>38.1</v>
       </c>
@@ -2372,6 +2462,9 @@
       <c r="D31">
         <v>-114.39941</v>
       </c>
+      <c r="F31" t="s">
+        <v>84</v>
+      </c>
       <c r="H31">
         <v>39.1</v>
       </c>
@@ -2428,6 +2521,9 @@
       <c r="D32">
         <v>-114.62857</v>
       </c>
+      <c r="F32" t="s">
+        <v>84</v>
+      </c>
       <c r="H32">
         <v>50</v>
       </c>
@@ -2481,6 +2577,9 @@
       <c r="D33">
         <v>-114.62865</v>
       </c>
+      <c r="F33" t="s">
+        <v>84</v>
+      </c>
       <c r="H33">
         <v>55.5</v>
       </c>
@@ -2534,6 +2633,9 @@
       <c r="D34">
         <v>-114.91002</v>
       </c>
+      <c r="F34" t="s">
+        <v>84</v>
+      </c>
       <c r="H34">
         <v>38</v>
       </c>
@@ -2587,6 +2689,9 @@
       <c r="D35">
         <v>-114.93224</v>
       </c>
+      <c r="F35" t="s">
+        <v>84</v>
+      </c>
       <c r="H35">
         <v>67.5</v>
       </c>
@@ -2640,6 +2745,9 @@
       <c r="D36">
         <v>-114.39941</v>
       </c>
+      <c r="F36" t="s">
+        <v>84</v>
+      </c>
       <c r="H36">
         <v>75</v>
       </c>
@@ -2696,6 +2804,9 @@
       <c r="D37">
         <v>-115.33841</v>
       </c>
+      <c r="F37" t="s">
+        <v>84</v>
+      </c>
       <c r="H37">
         <v>57.7</v>
       </c>
@@ -2749,6 +2860,9 @@
       <c r="D38">
         <v>-113.86163</v>
       </c>
+      <c r="F38" t="s">
+        <v>84</v>
+      </c>
       <c r="H38">
         <v>46.9</v>
       </c>
@@ -2802,6 +2916,9 @@
       <c r="D39">
         <v>-113.93984</v>
       </c>
+      <c r="F39" t="s">
+        <v>84</v>
+      </c>
       <c r="H39">
         <v>45.7</v>
       </c>
@@ -2858,6 +2975,9 @@
       <c r="D40">
         <v>-113.5077</v>
       </c>
+      <c r="F40" t="s">
+        <v>84</v>
+      </c>
       <c r="H40">
         <v>59.6</v>
       </c>
@@ -2914,6 +3034,9 @@
       <c r="D41">
         <v>-114.85699</v>
       </c>
+      <c r="F41" t="s">
+        <v>84</v>
+      </c>
       <c r="H41">
         <v>72</v>
       </c>
@@ -2967,6 +3090,9 @@
       <c r="D42">
         <v>-114.8268</v>
       </c>
+      <c r="F42" t="s">
+        <v>84</v>
+      </c>
       <c r="H42">
         <v>58.8</v>
       </c>
@@ -3019,6 +3145,9 @@
       </c>
       <c r="D43">
         <v>-114.8268</v>
+      </c>
+      <c r="F43" t="s">
+        <v>84</v>
       </c>
       <c r="H43">
         <v>58.5</v>
